--- a/artfynd/A 5950-2024 artfynd.xlsx
+++ b/artfynd/A 5950-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130200356</v>
       </c>
       <c r="B2" t="n">
-        <v>75073</v>
+        <v>75158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130200351</v>
       </c>
       <c r="B3" t="n">
-        <v>58575</v>
+        <v>58660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5950-2024 artfynd.xlsx
+++ b/artfynd/A 5950-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130200356</v>
       </c>
       <c r="B2" t="n">
-        <v>75158</v>
+        <v>75161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5950-2024 artfynd.xlsx
+++ b/artfynd/A 5950-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130200356</v>
       </c>
       <c r="B2" t="n">
-        <v>75161</v>
+        <v>75187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130200351</v>
       </c>
       <c r="B3" t="n">
-        <v>58660</v>
+        <v>58686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5950-2024 artfynd.xlsx
+++ b/artfynd/A 5950-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130200356</v>
       </c>
       <c r="B2" t="n">
-        <v>75187</v>
+        <v>75189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130200351</v>
       </c>
       <c r="B3" t="n">
-        <v>58686</v>
+        <v>58688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5950-2024 artfynd.xlsx
+++ b/artfynd/A 5950-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130200356</v>
+        <v>130200346</v>
       </c>
       <c r="B2" t="n">
-        <v>75189</v>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>103, Sk</t>
+          <t>113, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438878</v>
+        <v>438842</v>
       </c>
       <c r="R2" t="n">
-        <v>6207847</v>
+        <v>6207849</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130200351</v>
+        <v>130201159</v>
       </c>
       <c r="B3" t="n">
-        <v>58688</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>108, Sk</t>
+          <t>2504, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438876</v>
+        <v>438837</v>
       </c>
       <c r="R3" t="n">
-        <v>6207868</v>
+        <v>6207872</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,6 +866,685 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130200356</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>103, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>438878</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6207847</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Träne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130201163</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2500, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>438868</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6207864</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Träne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130200348</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>111, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>438849</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6207858</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Träne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130200351</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>108, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>438876</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6207868</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Träne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130200354</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101896</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>105, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>438865</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6207853</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Träne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130200350</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98968</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221918</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lundvårlök</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Gagea spathacea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hayne) Salisb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>109, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>438866</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6207856</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Träne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130200353</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>106, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>438874</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6207852</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Träne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
